--- a/data/hardtail/Esker Lorax Ti 2025.xlsx
+++ b/data/hardtail/Esker Lorax Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44369658-4BB3-7C4F-BCCF-F68ED9942B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70212262-8244-3548-B303-4282090301BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7380" yWindow="500" windowWidth="20520" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -272,18 +272,6 @@
     <t>https://eskercycles.com/pages/lorax-ti</t>
   </si>
   <si>
-    <t>S1/SM </t>
-  </si>
-  <si>
-    <t>S2/MD </t>
-  </si>
-  <si>
-    <t>S3/LG </t>
-  </si>
-  <si>
-    <t>S4/XL </t>
-  </si>
-  <si>
     <t>Effective TT Length</t>
   </si>
   <si>
@@ -363,6 +351,18 @@
   </si>
   <si>
     <t>us</t>
+  </si>
+  <si>
+    <t>S1/SM</t>
+  </si>
+  <si>
+    <t>S2/MD</t>
+  </si>
+  <si>
+    <t>S3/LG</t>
+  </si>
+  <si>
+    <t>S4/XL</t>
   </si>
 </sst>
 </file>
@@ -806,7 +806,7 @@
         <v>71</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -817,16 +817,16 @@
         <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -834,7 +834,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C9" s="3">
         <v>537</v>
@@ -854,7 +854,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C10" s="3">
         <v>365</v>
@@ -874,7 +874,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C11" s="3">
         <v>600</v>
@@ -894,7 +894,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C12" s="3">
         <v>68</v>
@@ -914,7 +914,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C13" s="3">
         <v>90</v>
@@ -934,7 +934,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C14" s="3">
         <v>74</v>
@@ -954,7 +954,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C15" s="3">
         <v>400</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C16" s="3">
         <v>300</v>
@@ -994,7 +994,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C17" s="3">
         <v>445</v>
@@ -1014,7 +1014,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C18" s="3">
         <v>44</v>
@@ -1034,7 +1034,7 @@
         <v>21</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C19" s="3">
         <v>495</v>
@@ -1054,7 +1054,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C20" s="3">
         <v>68</v>
@@ -1074,7 +1074,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C21" s="3">
         <v>1075</v>
@@ -1094,7 +1094,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C22" s="3">
         <v>60</v>
@@ -1112,7 +1112,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
@@ -1293,19 +1293,19 @@
         <v>73</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1313,7 +1313,7 @@
         <v>74</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1321,7 +1321,7 @@
         <v>75</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1406,7 +1406,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1427,7 +1427,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1557,7 +1557,7 @@
         <v>70</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
